--- a/config/Config/Data/技能.xlsx
+++ b/config/Config/Data/技能.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="456">
   <si>
     <t>##var</t>
   </si>
@@ -93,10 +93,10 @@
     <t>campus</t>
   </si>
   <si>
-    <t>壮胆</t>
-  </si>
-  <si>
-    <t>短时攻击提升（校园技，全员可学向）</t>
+    <t>课间壮胆</t>
+  </si>
+  <si>
+    <t>课间吹一波：短时攻击上升。全员都能学的课间绝活。</t>
   </si>
   <si>
     <t>Active|Campus</t>
@@ -114,10 +114,10 @@
     <t>CS_lixin</t>
   </si>
   <si>
-    <t>搏一把</t>
-  </si>
-  <si>
-    <t>高风险暴击向普攻强化（游戏民工本色）</t>
+    <t>今晚必红</t>
+  </si>
+  <si>
+    <t>游戏民工本色：赌一把高爆发，输赢都在这一刀。工牌绝活。</t>
   </si>
   <si>
     <t>Active|Job</t>
@@ -132,10 +132,10 @@
     <t>cs_lixin_crunch</t>
   </si>
   <si>
-    <t>肝帝冲刺</t>
-  </si>
-  <si>
-    <t>短时移速与攻速提升，透支后轻微自伤</t>
+    <t>通宵肝穿</t>
+  </si>
+  <si>
+    <t>ddl 面前人会飞：短暂又快又疼，透支后自己挨一下。工牌绝活。</t>
   </si>
   <si>
     <t>cs_lixin_crunch_buff|cs_lixin_crunch_selfhit</t>
@@ -150,10 +150,10 @@
     <t>CS_ayun</t>
   </si>
   <si>
-    <t>算力过载</t>
-  </si>
-  <si>
-    <t>锁定一名精英：减速并提高对其伤害（硕就业技）</t>
+    <t>把服务器打满</t>
+  </si>
+  <si>
+    <t>硕才肯使的绝活：点名一个硬茬减速，并专打他。晚毕业更值钱。</t>
   </si>
   <si>
     <t>cs_ayun_overload_slow|cs_ayun_overload_mark</t>
@@ -171,7 +171,7 @@
     <t>拆了重装</t>
   </si>
   <si>
-    <t>对精英高防巨伤，小怪概率解体（博就业技核心）</t>
+    <t>博士天花板：硬茬往死里拆，杂兵有机会直接解体。晚五年才给。</t>
   </si>
   <si>
     <t>xiebo_dismantle_dmg|xiebo_dismantle_break</t>
@@ -183,10 +183,10 @@
     <t>xiebo_patch</t>
   </si>
   <si>
-    <t>应急维修</t>
-  </si>
-  <si>
-    <t>友军铁皮盾</t>
+    <t>胶带先顶住</t>
+  </si>
+  <si>
+    <t>现场维修哲学：给兄弟糊一层铁皮盾。工牌绝活。</t>
   </si>
   <si>
     <t>xiebo_patch_shield</t>
@@ -198,10 +198,10 @@
     <t>xiebo_torque</t>
   </si>
   <si>
-    <t>扭矩全开</t>
-  </si>
-  <si>
-    <t>短时自身破甲加深，召唤工程机械影（博士强化位）</t>
+    <t>油门踩穿</t>
+  </si>
+  <si>
+    <t>扭矩拉满再叫挖机：自己破甲加深，并召唤工程影。博士强化位。</t>
   </si>
   <si>
     <t>xiebo_torque_buff|xiebo_torque_summon</t>
@@ -216,994 +216,1114 @@
     <t>GWY_wang</t>
   </si>
   <si>
+    <t>公章一盖</t>
+  </si>
+  <si>
+    <t>往旁边一站就有编制气场：附近兄弟攻击悄悄上涨。挂机也有用。</t>
+  </si>
+  <si>
+    <t>Passive|Job</t>
+  </si>
+  <si>
+    <t>gwy_wang_aura_buff</t>
+  </si>
+  <si>
+    <t>skill_civil_aura</t>
+  </si>
+  <si>
+    <t>dr_chen_heal</t>
+  </si>
+  <si>
+    <t>Dr_chen</t>
+  </si>
+  <si>
+    <t>有事喊我</t>
+  </si>
+  <si>
+    <t>先把人救醒，再喊热心市民真上。工牌绝活。</t>
+  </si>
+  <si>
+    <t>dr_chen_heal_hp|dr_chen_heal_summon</t>
+  </si>
+  <si>
+    <t>skill_clinic_heal</t>
+  </si>
+  <si>
+    <t>dr_xiao_drunk</t>
+  </si>
+  <si>
+    <t>Dr_xiao</t>
+  </si>
+  <si>
+    <t>摔杯为号</t>
+  </si>
+  <si>
+    <t>肖医生喝到上限，不再劝酒，摔杯为号。状态max</t>
+  </si>
+  <si>
+    <t>酒过三巡不再劝：杯子一摔，近敌发憷，兄弟聚成反击圈。</t>
+  </si>
+  <si>
+    <t>dr_xiao_drunk_fear|dr_xiao_drunk_max|dr_xiao_drunk_rally</t>
+  </si>
+  <si>
+    <t>skill_cup_signal</t>
+  </si>
+  <si>
+    <t>dr_xiao_ortho</t>
+  </si>
+  <si>
+    <t>德国骨科到了</t>
+  </si>
+  <si>
+    <t>复位手法比解释快：短时回血并给自己一层护盾。</t>
+  </si>
+  <si>
+    <t>dr_xiao_ortho_heal|dr_xiao_ortho_shield</t>
+  </si>
+  <si>
+    <t>skill_ortho</t>
+  </si>
+  <si>
+    <t>tm_yugu_smash</t>
+  </si>
+  <si>
+    <t>TM_yugu</t>
+  </si>
+  <si>
+    <t>粪桶外交</t>
+  </si>
+  <si>
+    <t>谕古：打生桩，叼工人粪桶，工地好好讲话没人听</t>
+  </si>
+  <si>
+    <t>工地讲话要响：抡范围砸，比好好说话有效。工牌绝活。</t>
+  </si>
+  <si>
+    <t>tm_yugu_smash_aoe</t>
+  </si>
+  <si>
+    <t>skill_civil_smash</t>
+  </si>
+  <si>
+    <t>tm_wantao_approve</t>
+  </si>
+  <si>
+    <t>TM_wantao</t>
+  </si>
+  <si>
+    <t>先卡着</t>
+  </si>
+  <si>
+    <t>甲方特长：点名一个让他慢下来，并变得更好打。工牌绝活。</t>
+  </si>
+  <si>
+    <t>tm_wantao_approve_slow|tm_wantao_approve_vuln</t>
+  </si>
+  <si>
+    <t>skill_civil_approve</t>
+  </si>
+  <si>
+    <t>bz_jihong_cost</t>
+  </si>
+  <si>
+    <t>BZ_jihong</t>
+  </si>
+  <si>
+    <t>这钱不能花</t>
+  </si>
+  <si>
+    <t>核算比拳头快：给兄弟们短时减伤。硕士财会盾。</t>
+  </si>
+  <si>
+    <t>bz_jihong_cost_shield</t>
+  </si>
+  <si>
+    <t>skill_finance_cost</t>
+  </si>
+  <si>
+    <t>bz_jihong_bonus</t>
+  </si>
+  <si>
+    <t>散烟时刻</t>
+  </si>
+  <si>
+    <t>烟一散，气势就来：挂着给全队加攻。工牌绝活。</t>
+  </si>
+  <si>
+    <t>bz_jihong_bonus_atk</t>
+  </si>
+  <si>
+    <t>skill_finance_bonus</t>
+  </si>
+  <si>
+    <t>yh_hangu_flow</t>
+  </si>
+  <si>
+    <t>YH_hangu</t>
+  </si>
+  <si>
+    <t>绿色通道</t>
+  </si>
+  <si>
+    <t>审核过了手脚就快：全队短时出手更勤快。工牌绝活。</t>
+  </si>
+  <si>
+    <t>yh_hangu_flow_buff</t>
+  </si>
+  <si>
+    <t>skill_bank_flow</t>
+  </si>
+  <si>
+    <t>yh_hangu_extend</t>
+  </si>
+  <si>
+    <t>先贷后还</t>
+  </si>
+  <si>
+    <t>资金先顶上：给自己一层信贷盾，下一波再算账。工牌绝活。</t>
+  </si>
+  <si>
+    <t>yh_hangu_extend_shield</t>
+  </si>
+  <si>
+    <t>skill_bank_extend</t>
+  </si>
+  <si>
+    <t>wuzi_boost</t>
+  </si>
+  <si>
+    <t>Energy_uzi</t>
+  </si>
+  <si>
+    <t>给机械兄弟加特效</t>
+  </si>
+  <si>
+    <t>储能硕士晚开的绝活：场上机械派系攻击和技能都更猛。</t>
+  </si>
+  <si>
+    <t>wuzi_boost_buff</t>
+  </si>
+  <si>
+    <t>skill_energy_boost</t>
+  </si>
+  <si>
+    <t>wuzi_grid</t>
+  </si>
+  <si>
+    <t>电闸拉上</t>
+  </si>
+  <si>
+    <t>应急供电：附近兄弟有盾，机械单位再加一层。晚毕业更厚。</t>
+  </si>
+  <si>
+    <t>wuzi_grid_shield|wuzi_grid_extra</t>
+  </si>
+  <si>
+    <t>skill_energy_grid</t>
+  </si>
+  <si>
+    <t>mow_eng_crush</t>
+  </si>
+  <si>
+    <t>eng_xie</t>
+  </si>
+  <si>
+    <t>挖机碾过去</t>
+  </si>
+  <si>
+    <t>工程影普攻：体积就是伤害。</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>mow_eng_crush_dmg</t>
+  </si>
+  <si>
+    <t>skill_crush</t>
+  </si>
+  <si>
+    <t>mow_hire_smash</t>
+  </si>
+  <si>
+    <t>temp_hire</t>
+  </si>
+  <si>
+    <t>工钱先欠着</t>
+  </si>
+  <si>
+    <t>临时工普攻：先干活，钱回头再说。</t>
+  </si>
+  <si>
+    <t>mow_hire_smash_dmg</t>
+  </si>
+  <si>
+    <t>skill_labor</t>
+  </si>
+  <si>
+    <t>fusion_overload</t>
+  </si>
+  <si>
+    <t>fusion</t>
+  </si>
+  <si>
+    <t>机油兑红牛</t>
+  </si>
+  <si>
+    <t>机械×能源同场连招：破甲和供电一起拉满。兄弟连招。</t>
+  </si>
+  <si>
+    <t>Active|Fusion</t>
+  </si>
+  <si>
+    <t>fusion_overload_buff</t>
+  </si>
+  <si>
+    <t>skill_fusion_overload</t>
+  </si>
+  <si>
+    <t>loot_stone_throw</t>
+  </si>
+  <si>
+    <t>loot</t>
+  </si>
+  <si>
+    <t>龙翔飞石</t>
+  </si>
+  <si>
+    <t>广场随手捡的：砸最近那个。地摊技，捡到算谁的。</t>
+  </si>
+  <si>
+    <t>loot_stone_throw_damage</t>
+  </si>
+  <si>
+    <t>loot_group_cheer</t>
+  </si>
+  <si>
+    <t>兄弟们上啊</t>
+  </si>
+  <si>
+    <t>喊一声附近都来劲。地摊技。</t>
+  </si>
+  <si>
+    <t>loot_group_cheer_buff</t>
+  </si>
+  <si>
+    <t>loot_first_aid</t>
+  </si>
+  <si>
+    <t>三块钱创口贴</t>
+  </si>
+  <si>
+    <t>药店最便宜那款：给附近受伤兄弟回一点。地摊技。</t>
+  </si>
+  <si>
+    <t>loot_first_aid_heal</t>
+  </si>
+  <si>
+    <t>energy_oban_ironhead</t>
+  </si>
+  <si>
+    <t>Energy_oban</t>
+  </si>
+  <si>
+    <t>铁头敲盆</t>
+  </si>
+  <si>
+    <t>欧版，高考毕业，铁头功，敲盆不会痛，高防</t>
+  </si>
+  <si>
+    <t>高考毕业就能用：铁头一敲，近敌发懵，自己盆一样厚。来得早。</t>
+  </si>
+  <si>
+    <t>energy_oban_ironhead_wave|energy_oban_ironhead_shield</t>
+  </si>
+  <si>
+    <t>skill_energy_ironhead</t>
+  </si>
+  <si>
+    <t>energy_oban_cherish</t>
+  </si>
+  <si>
+    <t>醉后惜缘</t>
+  </si>
+  <si>
+    <t>欧版，就业后，喝醉酒，谈恋爱，教育大家要懂得珍惜</t>
+  </si>
+  <si>
+    <t>酒后认真劝人：给附近兄弟盾和士气。就业后才肯掏心窝。</t>
+  </si>
+  <si>
+    <t>energy_oban_cherish_shield|energy_oban_cherish_buff</t>
+  </si>
+  <si>
+    <t>skill_energy_cherish</t>
+  </si>
+  <si>
+    <t>cs_ayun_dantiao</t>
+  </si>
+  <si>
+    <t>来单挑啊</t>
+  </si>
+  <si>
+    <t>啊允，进入zone状态，选择目标进行决斗单挑，本身属性提高10%，且对指定敌人伤害提高24%</t>
+  </si>
+  <si>
+    <t>遇强则强：自己进入 zone，点谁打谁，伤害再加一截。课间就能使。</t>
+  </si>
+  <si>
+    <t>cs_ayun_dantiao_zone|cs_ayun_dantiao_hit</t>
+  </si>
+  <si>
+    <t>skill_ayun_dantiao</t>
+  </si>
+  <si>
+    <t>cs_ayun_gaoliao</t>
+  </si>
+  <si>
+    <t>告料冲锋</t>
+  </si>
+  <si>
+    <t>阿允，喝醉酒吐了，匹配指挥官，指挥官指哪，他就和别人拼了，随机带走一个残血。</t>
+  </si>
+  <si>
+    <t>队友一指，他连吐带冲：专打被点名的那个，残血更好收。工牌绝活。</t>
+  </si>
+  <si>
+    <t>cs_ayun_gaoliao_hit|cs_ayun_gaoliao_rush</t>
+  </si>
+  <si>
+    <t>skill_gaoliao</t>
+  </si>
+  <si>
+    <t>tm_junjun_inspect</t>
+  </si>
+  <si>
+    <t>TM_junjun</t>
+  </si>
+  <si>
+    <t>安全帽必须戴</t>
+  </si>
+  <si>
+    <t>三方一来先圈隐患：范围内敌人减速，兄弟发到整改护具。</t>
+  </si>
+  <si>
+    <t>tm_junjun_inspect_slow|tm_junjun_inspect_shield</t>
+  </si>
+  <si>
+    <t>skill_civil_inspect</t>
+  </si>
+  <si>
+    <t>bus_laizhen_mobilize</t>
+  </si>
+  <si>
+    <t>Bus_laizhen</t>
+  </si>
+  <si>
+    <t>群里@所有人</t>
+  </si>
+  <si>
+    <t>创业组织力：立刻拉一个临时工，并给附近兄弟开工士气。</t>
+  </si>
+  <si>
+    <t>bus_laizhen_mobilize_hire|bus_laizhen_mobilize_buff</t>
+  </si>
+  <si>
+    <t>skill_business_mobilize</t>
+  </si>
+  <si>
+    <t>bus_longtou_turnaround</t>
+  </si>
+  <si>
+    <t>Bus_longtou</t>
+  </si>
+  <si>
+    <t>账上先好看</t>
+  </si>
+  <si>
+    <t>厂二代扭亏：先盾后打，现金流顶住再反攻。</t>
+  </si>
+  <si>
+    <t>bus_longtou_turnaround_shield|bus_longtou_turnaround_buff</t>
+  </si>
+  <si>
+    <t>skill_factory_turnaround</t>
+  </si>
+  <si>
+    <t>fusion_joint_inspection</t>
+  </si>
+  <si>
+    <t>安全帽会议</t>
+  </si>
+  <si>
+    <t>土木×公职联合验收：施工区减速，兄弟发护具。兄弟连招。</t>
+  </si>
+  <si>
+    <t>fusion_joint_inspection_slow|fusion_joint_inspection_shield</t>
+  </si>
+  <si>
+    <t>skill_fusion_inspection</t>
+  </si>
+  <si>
+    <t>fusion_supply_chain</t>
+  </si>
+  <si>
+    <t>货没出钱先响</t>
+  </si>
+  <si>
+    <t>创业×能源接通：全队开工加速，再临时补一个人。兄弟连招。</t>
+  </si>
+  <si>
+    <t>fusion_supply_chain_buff|fusion_supply_chain_hire</t>
+  </si>
+  <si>
+    <t>skill_fusion_supply_chain</t>
+  </si>
+  <si>
+    <t>tm_paopao_bargain</t>
+  </si>
+  <si>
+    <t>TM_PaoPao</t>
+  </si>
+  <si>
+    <t>再便宜两块</t>
+  </si>
+  <si>
+    <t>商务先把订金捂在自己身上，再对锁定目标敲一笔成交。搞钱绝活。</t>
+  </si>
+  <si>
+    <t>tm_paopao_bargain_shield|tm_paopao_bargain_hit</t>
+  </si>
+  <si>
+    <t>skill_paopao_bargain</t>
+  </si>
+  <si>
+    <t>mow_old_help</t>
+  </si>
+  <si>
+    <t>temp_old</t>
+  </si>
+  <si>
+    <t>真上</t>
+  </si>
+  <si>
+    <t>热心市民普攻：有事就是他们有事。</t>
+  </si>
+  <si>
+    <t>mow_old_help_dmg</t>
+  </si>
+  <si>
+    <t>kind</t>
+  </si>
+  <si>
+    <t>target</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>ratio</t>
+  </si>
+  <si>
+    <t>duration</t>
+  </si>
+  <si>
+    <t>radius</t>
+  </si>
+  <si>
+    <t>buff_id</t>
+  </si>
+  <si>
+    <t>summon_role_id</t>
+  </si>
+  <si>
+    <t>vfx_key</t>
+  </si>
+  <si>
+    <t>sfx_key</t>
+  </si>
+  <si>
+    <t>anim_trigger</t>
+  </si>
+  <si>
+    <t>comment</t>
+  </si>
+  <si>
+    <t>ESkillEffectKind</t>
+  </si>
+  <si>
+    <t>EEffectTarget</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>目标</t>
+  </si>
+  <si>
+    <t>主数值</t>
+  </si>
+  <si>
+    <t>倍率概率</t>
+  </si>
+  <si>
+    <t>持续秒</t>
+  </si>
+  <si>
+    <t>半径</t>
+  </si>
+  <si>
+    <t>BuffId</t>
+  </si>
+  <si>
+    <t>召唤角色</t>
+  </si>
+  <si>
+    <t>特效</t>
+  </si>
+  <si>
+    <t>音效</t>
+  </si>
+  <si>
+    <t>动画</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>AddBuff</t>
+  </si>
+  <si>
+    <t>Self</t>
+  </si>
+  <si>
+    <t>fx_buff_atk</t>
+  </si>
+  <si>
+    <t>sfx_buff</t>
+  </si>
+  <si>
+    <t>buff</t>
+  </si>
+  <si>
+    <t>攻击+15% 5秒</t>
+  </si>
+  <si>
+    <t>InstantDamage</t>
+  </si>
+  <si>
+    <t>Enemy</t>
+  </si>
+  <si>
+    <t>fx_crit</t>
+  </si>
+  <si>
+    <t>sfx_hit</t>
+  </si>
+  <si>
+    <t>attack</t>
+  </si>
+  <si>
+    <t>搏一把暴击倍率</t>
+  </si>
+  <si>
+    <t>cs_lixin_crunch_buff</t>
+  </si>
+  <si>
+    <t>fx_buff_spd</t>
+  </si>
+  <si>
+    <t>肝帝移速攻速</t>
+  </si>
+  <si>
+    <t>cs_lixin_crunch_selfhit</t>
+  </si>
+  <si>
+    <t>fx_overwork</t>
+  </si>
+  <si>
+    <t>hit</t>
+  </si>
+  <si>
+    <t>肝帝自伤</t>
+  </si>
+  <si>
+    <t>cs_ayun_overload_slow</t>
+  </si>
+  <si>
+    <t>fx_slow</t>
+  </si>
+  <si>
+    <t>sfx_algo</t>
+  </si>
+  <si>
+    <t>skill</t>
+  </si>
+  <si>
+    <t>算力减速</t>
+  </si>
+  <si>
+    <t>cs_ayun_overload_mark</t>
+  </si>
+  <si>
+    <t>fx_mark</t>
+  </si>
+  <si>
+    <t>对标记精英伤害+</t>
+  </si>
+  <si>
+    <t>xiebo_dismantle_dmg</t>
+  </si>
+  <si>
+    <t>fx_dismantle</t>
+  </si>
+  <si>
+    <t>sfx_metal</t>
+  </si>
+  <si>
+    <t>拆了重装高防倍率</t>
+  </si>
+  <si>
+    <t>xiebo_dismantle_break</t>
+  </si>
+  <si>
+    <t>fx_dismantle_kill</t>
+  </si>
+  <si>
+    <t>sfx_break</t>
+  </si>
+  <si>
+    <t>解体秒杀位</t>
+  </si>
+  <si>
+    <t>Shield</t>
+  </si>
+  <si>
+    <t>Ally</t>
+  </si>
+  <si>
+    <t>fx_shield</t>
+  </si>
+  <si>
+    <t>sfx_weld</t>
+  </si>
+  <si>
+    <t>铁皮盾</t>
+  </si>
+  <si>
+    <t>xiebo_torque_buff</t>
+  </si>
+  <si>
+    <t>fx_torque</t>
+  </si>
+  <si>
+    <t>扭矩破甲加深</t>
+  </si>
+  <si>
+    <t>xiebo_torque_summon</t>
+  </si>
+  <si>
+    <t>Summon</t>
+  </si>
+  <si>
+    <t>fx_summon</t>
+  </si>
+  <si>
+    <t>sfx_engine</t>
+  </si>
+  <si>
+    <t>召唤工程影</t>
+  </si>
+  <si>
+    <t>AllyAoe</t>
+  </si>
+  <si>
+    <t>fx_aura</t>
+  </si>
+  <si>
+    <t>idle</t>
+  </si>
+  <si>
     <t>体制光环</t>
   </si>
   <si>
-    <t>周围友军攻击提升</t>
-  </si>
-  <si>
-    <t>Passive|Job</t>
-  </si>
-  <si>
-    <t>gwy_wang_aura_buff</t>
-  </si>
-  <si>
-    <t>skill_civil_aura</t>
-  </si>
-  <si>
-    <t>dr_chen_heal</t>
-  </si>
-  <si>
-    <t>Dr_chen</t>
+    <t>dr_chen_heal_hp</t>
+  </si>
+  <si>
+    <t>Heal</t>
+  </si>
+  <si>
+    <t>fx_heal</t>
+  </si>
+  <si>
+    <t>sfx_heal</t>
   </si>
   <si>
     <t>民心急救</t>
   </si>
   <si>
-    <t>治疗友军</t>
-  </si>
-  <si>
-    <t>dr_chen_heal_hp</t>
-  </si>
-  <si>
-    <t>skill_clinic_heal</t>
-  </si>
-  <si>
-    <t>dr_xiao_drunk</t>
-  </si>
-  <si>
-    <t>Dr_xiao</t>
-  </si>
-  <si>
-    <t>摔杯为号</t>
-  </si>
-  <si>
-    <t>肖医生喝到上限，不再劝酒，摔杯为号。状态max</t>
-  </si>
-  <si>
-    <t>状态喝满后不再劝酒：摔杯震慑近敌，并把附近兄弟聚成反击阵势</t>
-  </si>
-  <si>
-    <t>dr_xiao_drunk_fear|dr_xiao_drunk_max|dr_xiao_drunk_rally</t>
-  </si>
-  <si>
-    <t>skill_cup_signal</t>
-  </si>
-  <si>
-    <t>dr_xiao_ortho</t>
-  </si>
-  <si>
-    <t>骨科复位</t>
-  </si>
-  <si>
-    <t>短时回血并护盾</t>
-  </si>
-  <si>
-    <t>dr_xiao_ortho_heal|dr_xiao_ortho_shield</t>
-  </si>
-  <si>
-    <t>skill_ortho</t>
-  </si>
-  <si>
-    <t>tm_yugu_smash</t>
-  </si>
-  <si>
-    <t>TM_yugu</t>
+    <t>EnemyAoe</t>
+  </si>
+  <si>
+    <t>fx_smash</t>
+  </si>
+  <si>
+    <t>sfx_smash</t>
   </si>
   <si>
     <t>工地砸</t>
   </si>
   <si>
-    <t>谕古：打生桩，叼工人粪桶，工地好好讲话没人听</t>
-  </si>
-  <si>
-    <t>范围伤害，叼一些粪桶样（项目经理一线视察）</t>
-  </si>
-  <si>
-    <t>tm_yugu_smash_aoe</t>
-  </si>
-  <si>
-    <t>skill_civil_smash</t>
-  </si>
-  <si>
-    <t>tm_wantao_approve</t>
-  </si>
-  <si>
-    <t>TM_wantao</t>
-  </si>
-  <si>
-    <t>项目审批</t>
-  </si>
-  <si>
-    <t>点名减速精英，制造困难，并使其易伤（甲方特色）</t>
-  </si>
-  <si>
-    <t>tm_wantao_approve_slow|tm_wantao_approve_vuln</t>
-  </si>
-  <si>
-    <t>skill_civil_approve</t>
-  </si>
-  <si>
-    <t>bz_jihong_cost</t>
-  </si>
-  <si>
-    <t>BZ_jihong</t>
-  </si>
-  <si>
-    <t>成本核算</t>
-  </si>
-  <si>
-    <t>友军短时减伤（财会盾）</t>
-  </si>
-  <si>
-    <t>bz_jihong_cost_shield</t>
-  </si>
-  <si>
-    <t>skill_finance_cost</t>
-  </si>
-  <si>
-    <t>bz_jihong_bonus</t>
-  </si>
-  <si>
-    <t>散烟时刻</t>
-  </si>
-  <si>
-    <t>给兄弟们分发大量香烟，提振士气（局内用攻击加成模拟）</t>
-  </si>
-  <si>
-    <t>bz_jihong_bonus_atk</t>
-  </si>
-  <si>
-    <t>skill_finance_bonus</t>
-  </si>
-  <si>
-    <t>yh_hangu_flow</t>
-  </si>
-  <si>
-    <t>YH_hangu</t>
-  </si>
-  <si>
-    <t>审核加速</t>
-  </si>
-  <si>
-    <t>全队短时攻击速度提升，技能CD缩减</t>
-  </si>
-  <si>
-    <t>yh_hangu_flow_buff</t>
-  </si>
-  <si>
-    <t>skill_bank_flow</t>
-  </si>
-  <si>
-    <t>yh_hangu_extend</t>
-  </si>
-  <si>
-    <t>信贷办理</t>
-  </si>
-  <si>
-    <t>可以为章节选择和购进时候，进行贷款透支操作</t>
-  </si>
-  <si>
-    <t>yh_hangu_extend_shield</t>
-  </si>
-  <si>
-    <t>skill_bank_extend</t>
-  </si>
-  <si>
-    <t>wuzi_boost</t>
-  </si>
-  <si>
-    <t>Energy_uzi</t>
-  </si>
-  <si>
-    <t>能源增幅</t>
-  </si>
-  <si>
-    <t>强化场上机械派系友军攻击与技能倍率</t>
-  </si>
-  <si>
-    <t>wuzi_boost_buff</t>
-  </si>
-  <si>
-    <t>skill_energy_boost</t>
-  </si>
-  <si>
-    <t>wuzi_grid</t>
-  </si>
-  <si>
-    <t>应急供电</t>
-  </si>
-  <si>
-    <t>友军范围护盾，机械单位额外一层</t>
-  </si>
-  <si>
-    <t>wuzi_grid_shield|wuzi_grid_extra</t>
-  </si>
-  <si>
-    <t>skill_energy_grid</t>
-  </si>
-  <si>
-    <t>mow_eng_crush</t>
-  </si>
-  <si>
-    <t>eng_xie</t>
-  </si>
-  <si>
-    <t>碾压</t>
+    <t>tm_wantao_approve_slow</t>
+  </si>
+  <si>
+    <t>fx_approve</t>
+  </si>
+  <si>
+    <t>sfx_stamp</t>
+  </si>
+  <si>
+    <t>审批减速</t>
+  </si>
+  <si>
+    <t>tm_wantao_approve_vuln</t>
+  </si>
+  <si>
+    <t>fx_vuln</t>
+  </si>
+  <si>
+    <t>审批易伤</t>
+  </si>
+  <si>
+    <t>dr_xiao_ortho_heal</t>
+  </si>
+  <si>
+    <t>骨科回血</t>
+  </si>
+  <si>
+    <t>dr_xiao_ortho_shield</t>
+  </si>
+  <si>
+    <t>骨科护盾</t>
+  </si>
+  <si>
+    <t>fx_hit</t>
   </si>
   <si>
     <t>工程影普攻</t>
   </si>
   <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>mow_eng_crush_dmg</t>
-  </si>
-  <si>
-    <t>skill_crush</t>
-  </si>
-  <si>
-    <t>mow_hire_smash</t>
-  </si>
-  <si>
-    <t>temp_hire</t>
-  </si>
-  <si>
-    <t>苦力砸</t>
-  </si>
-  <si>
     <t>临时工普攻</t>
   </si>
   <si>
-    <t>mow_hire_smash_dmg</t>
-  </si>
-  <si>
-    <t>skill_labor</t>
-  </si>
-  <si>
-    <t>fusion_overload</t>
-  </si>
-  <si>
-    <t>fusion</t>
+    <t>fx_ledger</t>
+  </si>
+  <si>
+    <t>sfx_coin</t>
+  </si>
+  <si>
+    <t>成本核算盾</t>
+  </si>
+  <si>
+    <t>fx_bonus</t>
+  </si>
+  <si>
+    <t>烟草红利常驻小攻</t>
+  </si>
+  <si>
+    <t>fx_cash</t>
+  </si>
+  <si>
+    <t>融通资金攻</t>
+  </si>
+  <si>
+    <t>fx_credit</t>
+  </si>
+  <si>
+    <t>信贷展期盾</t>
+  </si>
+  <si>
+    <t>fx_power</t>
+  </si>
+  <si>
+    <t>sfx_hum</t>
+  </si>
+  <si>
+    <t>能源增幅(机械吃满)</t>
+  </si>
+  <si>
+    <t>wuzi_grid_shield</t>
+  </si>
+  <si>
+    <t>fx_grid</t>
+  </si>
+  <si>
+    <t>应急供电盾</t>
+  </si>
+  <si>
+    <t>wuzi_grid_extra</t>
+  </si>
+  <si>
+    <t>fx_grid_extra</t>
+  </si>
+  <si>
+    <t>机械额外供电</t>
+  </si>
+  <si>
+    <t>fx_fusion</t>
   </si>
   <si>
     <t>重装过载</t>
   </si>
   <si>
-    <t>机械×能源羁绊：短时破甲与供电半径同时提升</t>
-  </si>
-  <si>
-    <t>Active|Fusion</t>
-  </si>
-  <si>
-    <t>fusion_overload_buff</t>
-  </si>
-  <si>
-    <t>skill_fusion_overload</t>
-  </si>
-  <si>
-    <t>loot_stone_throw</t>
-  </si>
-  <si>
-    <t>loot</t>
-  </si>
-  <si>
-    <t>飞石</t>
-  </si>
-  <si>
-    <t>捡起石块砸向最近敌人</t>
-  </si>
-  <si>
-    <t>loot_stone_throw_damage</t>
-  </si>
-  <si>
-    <t>loot_group_cheer</t>
-  </si>
-  <si>
-    <t>组队壮胆</t>
-  </si>
-  <si>
-    <t>短时间提高附近兄弟攻击</t>
-  </si>
-  <si>
-    <t>loot_group_cheer_buff</t>
-  </si>
-  <si>
-    <t>loot_first_aid</t>
-  </si>
-  <si>
-    <t>临时急救</t>
-  </si>
-  <si>
-    <t>治疗附近受伤兄弟</t>
-  </si>
-  <si>
-    <t>loot_first_aid_heal</t>
-  </si>
-  <si>
-    <t>energy_oban_ironhead</t>
-  </si>
-  <si>
-    <t>Energy_oban</t>
-  </si>
-  <si>
-    <t>铁头敲盆</t>
-  </si>
-  <si>
-    <t>欧版，高考毕业，铁头功，敲盆不会痛，高防</t>
-  </si>
-  <si>
-    <t>铁头敲盆震开近敌并给自己加厚护盾，高考毕业后较早成型</t>
-  </si>
-  <si>
-    <t>energy_oban_ironhead_wave|energy_oban_ironhead_shield</t>
-  </si>
-  <si>
-    <t>skill_energy_ironhead</t>
-  </si>
-  <si>
-    <t>energy_oban_cherish</t>
-  </si>
-  <si>
-    <t>醉后惜缘</t>
-  </si>
-  <si>
-    <t>欧版，就业后，喝醉酒，谈恋爱，教育大家要懂得珍惜</t>
-  </si>
-  <si>
-    <t>酒后认真劝大家珍惜眼前人，为附近兄弟提供护盾和士气</t>
-  </si>
-  <si>
-    <t>energy_oban_cherish_shield|energy_oban_cherish_buff</t>
-  </si>
-  <si>
-    <t>skill_energy_cherish</t>
-  </si>
-  <si>
-    <t>cs_ayun_gaoliao</t>
-  </si>
-  <si>
-    <t>告料</t>
-  </si>
-  <si>
-    <t>阿允，喝醉酒吐了，匹配指挥官，指挥官指哪，他就和别人拼了，随机带走一个残血。</t>
-  </si>
-  <si>
-    <t>听从队友点名冲向一个敌人狠狠干，残血目标更容易被带走</t>
-  </si>
-  <si>
-    <t>cs_ayun_gaoliao_hit|cs_ayun_gaoliao_rush</t>
-  </si>
-  <si>
-    <t>skill_gaoliao</t>
-  </si>
-  <si>
-    <t>tm_junjun_inspect</t>
-  </si>
-  <si>
-    <t>TM_junjun</t>
-  </si>
-  <si>
-    <t>三方巡检</t>
-  </si>
-  <si>
-    <t>圈出施工隐患区，减速范围敌人并给附近兄弟发放整改护具</t>
-  </si>
-  <si>
-    <t>tm_junjun_inspect_slow|tm_junjun_inspect_shield</t>
-  </si>
-  <si>
-    <t>skill_civil_inspect</t>
-  </si>
-  <si>
-    <t>bus_laizhen_mobilize</t>
-  </si>
-  <si>
-    <t>Bus_laizhen</t>
-  </si>
-  <si>
-    <t>拉人开工</t>
-  </si>
-  <si>
-    <t>创业能手迅速拉起临时班底，并提升附近兄弟的开工士气</t>
-  </si>
-  <si>
-    <t>bus_laizhen_mobilize_hire|bus_laizhen_mobilize_buff</t>
-  </si>
-  <si>
-    <t>skill_business_mobilize</t>
-  </si>
-  <si>
-    <t>bus_longtou_turnaround</t>
-  </si>
-  <si>
-    <t>Bus_longtou</t>
-  </si>
-  <si>
-    <t>扭亏为盈</t>
-  </si>
-  <si>
-    <t>重启厂线并兜住现金流，为附近兄弟同时提供护盾与反攻增益</t>
-  </si>
-  <si>
-    <t>bus_longtou_turnaround_shield|bus_longtou_turnaround_buff</t>
-  </si>
-  <si>
-    <t>skill_factory_turnaround</t>
-  </si>
-  <si>
-    <t>fusion_joint_inspection</t>
-  </si>
-  <si>
-    <t>联合验收</t>
-  </si>
-  <si>
-    <t>土木与公共治理联合验收：敌方施工区减速，兄弟获得安全护具</t>
-  </si>
-  <si>
-    <t>fusion_joint_inspection_slow|fusion_joint_inspection_shield</t>
-  </si>
-  <si>
-    <t>skill_fusion_inspection</t>
-  </si>
-  <si>
-    <t>fusion_supply_chain</t>
-  </si>
-  <si>
-    <t>产销一体</t>
-  </si>
-  <si>
-    <t>创业渠道连接能源产能：全队提速开工，并临时补充一名生产人员</t>
-  </si>
-  <si>
-    <t>fusion_supply_chain_buff|fusion_supply_chain_hire</t>
-  </si>
-  <si>
-    <t>skill_fusion_supply_chain</t>
-  </si>
-  <si>
-    <t>kind</t>
-  </si>
-  <si>
-    <t>target</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>ratio</t>
-  </si>
-  <si>
-    <t>duration</t>
-  </si>
-  <si>
-    <t>radius</t>
-  </si>
-  <si>
-    <t>buff_id</t>
-  </si>
-  <si>
-    <t>summon_role_id</t>
-  </si>
-  <si>
-    <t>vfx_key</t>
-  </si>
-  <si>
-    <t>sfx_key</t>
-  </si>
-  <si>
-    <t>anim_trigger</t>
-  </si>
-  <si>
-    <t>comment</t>
-  </si>
-  <si>
-    <t>ESkillEffectKind</t>
-  </si>
-  <si>
-    <t>EEffectTarget</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>类型</t>
-  </si>
-  <si>
-    <t>目标</t>
-  </si>
-  <si>
-    <t>主数值</t>
-  </si>
-  <si>
-    <t>倍率概率</t>
-  </si>
-  <si>
-    <t>持续秒</t>
-  </si>
-  <si>
-    <t>半径</t>
-  </si>
-  <si>
-    <t>BuffId</t>
-  </si>
-  <si>
-    <t>召唤角色</t>
-  </si>
-  <si>
-    <t>特效</t>
-  </si>
-  <si>
-    <t>音效</t>
-  </si>
-  <si>
-    <t>动画</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>AddBuff</t>
-  </si>
-  <si>
-    <t>Self</t>
-  </si>
-  <si>
-    <t>fx_buff_atk</t>
-  </si>
-  <si>
-    <t>sfx_buff</t>
-  </si>
-  <si>
-    <t>buff</t>
-  </si>
-  <si>
-    <t>攻击+15% 5秒</t>
-  </si>
-  <si>
-    <t>InstantDamage</t>
-  </si>
-  <si>
-    <t>Enemy</t>
-  </si>
-  <si>
-    <t>fx_crit</t>
-  </si>
-  <si>
-    <t>sfx_hit</t>
-  </si>
-  <si>
-    <t>attack</t>
-  </si>
-  <si>
-    <t>搏一把暴击倍率</t>
-  </si>
-  <si>
-    <t>cs_lixin_crunch_buff</t>
-  </si>
-  <si>
-    <t>fx_buff_spd</t>
-  </si>
-  <si>
-    <t>肝帝移速攻速</t>
-  </si>
-  <si>
-    <t>cs_lixin_crunch_selfhit</t>
-  </si>
-  <si>
-    <t>fx_overwork</t>
-  </si>
-  <si>
-    <t>hit</t>
-  </si>
-  <si>
-    <t>肝帝自伤</t>
-  </si>
-  <si>
-    <t>cs_ayun_overload_slow</t>
-  </si>
-  <si>
-    <t>fx_slow</t>
-  </si>
-  <si>
-    <t>sfx_algo</t>
-  </si>
-  <si>
-    <t>skill</t>
-  </si>
-  <si>
-    <t>算力减速</t>
-  </si>
-  <si>
-    <t>cs_ayun_overload_mark</t>
-  </si>
-  <si>
-    <t>fx_mark</t>
-  </si>
-  <si>
-    <t>对标记精英伤害+</t>
-  </si>
-  <si>
-    <t>xiebo_dismantle_dmg</t>
-  </si>
-  <si>
-    <t>fx_dismantle</t>
-  </si>
-  <si>
-    <t>sfx_metal</t>
-  </si>
-  <si>
-    <t>拆了重装高防倍率</t>
-  </si>
-  <si>
-    <t>xiebo_dismantle_break</t>
-  </si>
-  <si>
-    <t>fx_dismantle_kill</t>
-  </si>
-  <si>
-    <t>sfx_break</t>
-  </si>
-  <si>
-    <t>解体秒杀位</t>
-  </si>
-  <si>
-    <t>Shield</t>
-  </si>
-  <si>
-    <t>Ally</t>
-  </si>
-  <si>
-    <t>fx_shield</t>
-  </si>
-  <si>
-    <t>sfx_weld</t>
-  </si>
-  <si>
-    <t>铁皮盾</t>
-  </si>
-  <si>
-    <t>xiebo_torque_buff</t>
-  </si>
-  <si>
-    <t>fx_torque</t>
-  </si>
-  <si>
-    <t>扭矩破甲加深</t>
-  </si>
-  <si>
-    <t>xiebo_torque_summon</t>
-  </si>
-  <si>
-    <t>Summon</t>
-  </si>
-  <si>
-    <t>fx_summon</t>
-  </si>
-  <si>
-    <t>sfx_engine</t>
-  </si>
-  <si>
-    <t>召唤工程影</t>
-  </si>
-  <si>
-    <t>AllyAoe</t>
-  </si>
-  <si>
-    <t>fx_aura</t>
-  </si>
-  <si>
-    <t>idle</t>
-  </si>
-  <si>
-    <t>Heal</t>
-  </si>
-  <si>
-    <t>fx_heal</t>
-  </si>
-  <si>
-    <t>sfx_heal</t>
-  </si>
-  <si>
-    <t>EnemyAoe</t>
-  </si>
-  <si>
-    <t>fx_smash</t>
-  </si>
-  <si>
-    <t>sfx_smash</t>
-  </si>
-  <si>
-    <t>tm_wantao_approve_slow</t>
-  </si>
-  <si>
-    <t>fx_approve</t>
-  </si>
-  <si>
-    <t>sfx_stamp</t>
-  </si>
-  <si>
-    <t>审批减速</t>
-  </si>
-  <si>
-    <t>tm_wantao_approve_vuln</t>
-  </si>
-  <si>
-    <t>fx_vuln</t>
-  </si>
-  <si>
-    <t>审批易伤</t>
-  </si>
-  <si>
-    <t>dr_xiao_ortho_heal</t>
-  </si>
-  <si>
-    <t>骨科回血</t>
-  </si>
-  <si>
-    <t>dr_xiao_ortho_shield</t>
-  </si>
-  <si>
-    <t>骨科护盾</t>
-  </si>
-  <si>
-    <t>fx_hit</t>
-  </si>
-  <si>
-    <t>fx_ledger</t>
-  </si>
-  <si>
-    <t>sfx_coin</t>
-  </si>
-  <si>
-    <t>成本核算盾</t>
-  </si>
-  <si>
-    <t>fx_bonus</t>
-  </si>
-  <si>
-    <t>烟草红利常驻小攻</t>
-  </si>
-  <si>
-    <t>fx_cash</t>
-  </si>
-  <si>
-    <t>融通资金攻</t>
-  </si>
-  <si>
-    <t>fx_credit</t>
-  </si>
-  <si>
-    <t>信贷展期盾</t>
+    <t>stone</t>
+  </si>
+  <si>
+    <t>临时掉落技能</t>
+  </si>
+  <si>
+    <t>cheer</t>
+  </si>
+  <si>
+    <t>first_aid</t>
+  </si>
+  <si>
+    <t>energy_oban_ironhead_wave</t>
+  </si>
+  <si>
+    <t>fx_basin_wave</t>
+  </si>
+  <si>
+    <t>敲盆震击近敌</t>
+  </si>
+  <si>
+    <t>energy_oban_ironhead_shield</t>
+  </si>
+  <si>
+    <t>fx_ironhead</t>
+  </si>
+  <si>
+    <t>铁头高防</t>
+  </si>
+  <si>
+    <t>energy_oban_cherish_shield</t>
+  </si>
+  <si>
+    <t>fx_cherish_shield</t>
+  </si>
+  <si>
+    <t>sfx_cheer</t>
+  </si>
+  <si>
+    <t>珍惜眼前人团队盾</t>
+  </si>
+  <si>
+    <t>energy_oban_cherish_buff</t>
+  </si>
+  <si>
+    <t>fx_cherish</t>
+  </si>
+  <si>
+    <t>附近兄弟攻击+12%</t>
+  </si>
+  <si>
+    <t>cs_ayun_gaoliao_hit</t>
+  </si>
+  <si>
+    <t>fx_gaoliao_hit</t>
+  </si>
+  <si>
+    <t>sfx_charge</t>
+  </si>
+  <si>
+    <t>点名单体重击；低血目标自然进入收割线</t>
+  </si>
+  <si>
+    <t>cs_ayun_gaoliao_rush</t>
+  </si>
+  <si>
+    <t>fx_gaoliao_rush</t>
+  </si>
+  <si>
+    <t>告料后短时攻击+20%</t>
+  </si>
+  <si>
+    <t>dr_xiao_drunk_fear</t>
+  </si>
+  <si>
+    <t>fx_cup_fear</t>
+  </si>
+  <si>
+    <t>sfx_cup_break</t>
+  </si>
+  <si>
+    <t>摔杯威慑减速30%</t>
+  </si>
+  <si>
+    <t>dr_xiao_drunk_max</t>
+  </si>
+  <si>
+    <t>fx_state_max</t>
+  </si>
+  <si>
+    <t>状态MAX，自身攻击+25%</t>
+  </si>
+  <si>
+    <t>dr_xiao_drunk_rally</t>
+  </si>
+  <si>
+    <t>fx_rally</t>
+  </si>
+  <si>
+    <t>聚拢兄弟以攻击阵势模拟</t>
+  </si>
+  <si>
+    <t>tm_junjun_inspect_slow</t>
+  </si>
+  <si>
+    <t>fx_inspect_zone</t>
+  </si>
+  <si>
+    <t>sfx_whistle</t>
+  </si>
+  <si>
+    <t>综合治理区域减速</t>
+  </si>
+  <si>
+    <t>tm_junjun_inspect_shield</t>
+  </si>
+  <si>
+    <t>fx_safety_gear</t>
+  </si>
+  <si>
+    <t>三方监理整改护具</t>
+  </si>
+  <si>
+    <t>bus_laizhen_mobilize_hire</t>
+  </si>
+  <si>
+    <t>fx_hire</t>
+  </si>
+  <si>
+    <t>召集一名临时工</t>
+  </si>
+  <si>
+    <t>bus_laizhen_mobilize_buff</t>
+  </si>
+  <si>
+    <t>fx_open_shop</t>
+  </si>
+  <si>
+    <t>开工士气攻击+12%</t>
+  </si>
+  <si>
+    <t>bus_longtou_turnaround_shield</t>
+  </si>
+  <si>
+    <t>fx_cashflow_shield</t>
+  </si>
+  <si>
+    <t>sfx_factory_start</t>
+  </si>
+  <si>
+    <t>现金流兜底团队盾</t>
+  </si>
+  <si>
+    <t>bus_longtou_turnaround_buff</t>
+  </si>
+  <si>
+    <t>fx_factory_restart</t>
+  </si>
+  <si>
+    <t>厂线重启攻击+16%</t>
+  </si>
+  <si>
+    <t>fusion_joint_inspection_slow</t>
+  </si>
+  <si>
+    <t>fx_joint_inspection</t>
+  </si>
+  <si>
+    <t>联合验收区域减速</t>
+  </si>
+  <si>
+    <t>fusion_joint_inspection_shield</t>
+  </si>
+  <si>
+    <t>fx_joint_safety</t>
+  </si>
+  <si>
+    <t>联合安全护具</t>
+  </si>
+  <si>
+    <t>fusion_supply_chain_buff</t>
+  </si>
+  <si>
+    <t>fx_supply_chain</t>
+  </si>
+  <si>
+    <t>产能与渠道联动攻击+25%</t>
+  </si>
+  <si>
+    <t>fusion_supply_chain_hire</t>
+  </si>
+  <si>
+    <t>产销联动临时生产人员</t>
+  </si>
+  <si>
+    <t>cs_ayun_dantiao_zone</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>fx_power</t>
-  </si>
-  <si>
-    <t>sfx_hum</t>
-  </si>
-  <si>
-    <t>能源增幅(机械吃满)</t>
-  </si>
-  <si>
-    <t>wuzi_grid_shield</t>
-  </si>
-  <si>
-    <t>fx_grid</t>
-  </si>
-  <si>
-    <t>应急供电盾</t>
-  </si>
-  <si>
-    <t>wuzi_grid_extra</t>
-  </si>
-  <si>
-    <t>fx_grid_extra</t>
-  </si>
-  <si>
-    <t>机械额外供电</t>
-  </si>
-  <si>
-    <t>fx_fusion</t>
-  </si>
-  <si>
-    <t>stone</t>
-  </si>
-  <si>
-    <t>临时掉落技能</t>
-  </si>
-  <si>
-    <t>cheer</t>
-  </si>
-  <si>
-    <t>first_aid</t>
-  </si>
-  <si>
-    <t>energy_oban_ironhead_wave</t>
-  </si>
-  <si>
-    <t>fx_basin_wave</t>
-  </si>
-  <si>
-    <t>敲盆震击近敌</t>
-  </si>
-  <si>
-    <t>energy_oban_ironhead_shield</t>
-  </si>
-  <si>
-    <t>fx_ironhead</t>
-  </si>
-  <si>
-    <t>铁头高防</t>
-  </si>
-  <si>
-    <t>energy_oban_cherish_shield</t>
-  </si>
-  <si>
-    <t>fx_cherish_shield</t>
-  </si>
-  <si>
-    <t>sfx_cheer</t>
-  </si>
-  <si>
-    <t>珍惜眼前人团队盾</t>
-  </si>
-  <si>
-    <t>energy_oban_cherish_buff</t>
-  </si>
-  <si>
-    <t>fx_cherish</t>
-  </si>
-  <si>
-    <t>附近兄弟攻击+12%</t>
-  </si>
-  <si>
-    <t>cs_ayun_gaoliao_hit</t>
-  </si>
-  <si>
-    <t>fx_gaoliao_hit</t>
-  </si>
-  <si>
-    <t>sfx_charge</t>
-  </si>
-  <si>
-    <t>点名单体重击；低血目标自然进入收割线</t>
-  </si>
-  <si>
-    <t>cs_ayun_gaoliao_rush</t>
-  </si>
-  <si>
-    <t>fx_gaoliao_rush</t>
-  </si>
-  <si>
-    <t>告料后短时攻击+20%</t>
-  </si>
-  <si>
-    <t>dr_xiao_drunk_fear</t>
-  </si>
-  <si>
-    <t>fx_cup_fear</t>
-  </si>
-  <si>
-    <t>sfx_cup_break</t>
-  </si>
-  <si>
-    <t>摔杯威慑减速30%</t>
-  </si>
-  <si>
-    <t>dr_xiao_drunk_max</t>
-  </si>
-  <si>
-    <t>fx_state_max</t>
-  </si>
-  <si>
-    <t>状态MAX，自身攻击+25%</t>
-  </si>
-  <si>
-    <t>dr_xiao_drunk_rally</t>
-  </si>
-  <si>
-    <t>fx_rally</t>
-  </si>
-  <si>
-    <t>聚拢兄弟以攻击阵势模拟</t>
-  </si>
-  <si>
-    <t>tm_junjun_inspect_slow</t>
-  </si>
-  <si>
-    <t>fx_inspect_zone</t>
-  </si>
-  <si>
-    <t>sfx_whistle</t>
-  </si>
-  <si>
-    <t>综合治理区域减速</t>
-  </si>
-  <si>
-    <t>tm_junjun_inspect_shield</t>
-  </si>
-  <si>
-    <t>fx_safety_gear</t>
-  </si>
-  <si>
-    <t>三方监理整改护具</t>
-  </si>
-  <si>
-    <t>bus_laizhen_mobilize_hire</t>
-  </si>
-  <si>
-    <t>fx_hire</t>
-  </si>
-  <si>
-    <t>召集一名临时工</t>
-  </si>
-  <si>
-    <t>bus_laizhen_mobilize_buff</t>
-  </si>
-  <si>
-    <t>fx_open_shop</t>
-  </si>
-  <si>
-    <t>开工士气攻击+12%</t>
-  </si>
-  <si>
-    <t>bus_longtou_turnaround_shield</t>
-  </si>
-  <si>
-    <t>fx_cashflow_shield</t>
-  </si>
-  <si>
-    <t>sfx_factory_start</t>
-  </si>
-  <si>
-    <t>现金流兜底团队盾</t>
-  </si>
-  <si>
-    <t>bus_longtou_turnaround_buff</t>
-  </si>
-  <si>
-    <t>fx_factory_restart</t>
-  </si>
-  <si>
-    <t>厂线重启攻击+16%</t>
-  </si>
-  <si>
-    <t>fusion_joint_inspection_slow</t>
-  </si>
-  <si>
-    <t>fx_joint_inspection</t>
-  </si>
-  <si>
-    <t>联合验收区域减速</t>
-  </si>
-  <si>
-    <t>fusion_joint_inspection_shield</t>
-  </si>
-  <si>
-    <t>fx_joint_safety</t>
-  </si>
-  <si>
-    <t>联合安全护具</t>
-  </si>
-  <si>
-    <t>fusion_supply_chain_buff</t>
-  </si>
-  <si>
-    <t>fx_supply_chain</t>
-  </si>
-  <si>
-    <t>产能与渠道联动攻击+25%</t>
-  </si>
-  <si>
-    <t>fusion_supply_chain_hire</t>
-  </si>
-  <si>
-    <t>产销联动临时生产人员</t>
+    <t>fx_zone</t>
+  </si>
+  <si>
+    <t>sfx_focus</t>
+  </si>
+  <si>
+    <t>zone 自身攻击+10%</t>
+  </si>
+  <si>
+    <t>cs_ayun_dantiao_hit</t>
+  </si>
+  <si>
+    <t>fx_duel</t>
+  </si>
+  <si>
+    <t>决斗一击，指定目标伤害+24%</t>
+  </si>
+  <si>
+    <t>tm_paopao_bargain_shield</t>
+  </si>
+  <si>
+    <t>fx_deposit</t>
+  </si>
+  <si>
+    <t>订金到账护盾</t>
+  </si>
+  <si>
+    <t>tm_paopao_bargain_hit</t>
+  </si>
+  <si>
+    <t>fx_deal</t>
+  </si>
+  <si>
+    <t>成交敲定</t>
+  </si>
+  <si>
+    <t>热心市民普攻</t>
+  </si>
+  <si>
+    <t>dr_chen_heal_summon</t>
+  </si>
+  <si>
+    <t>热心市民真上</t>
   </si>
   <si>
     <t>required_tags</t>
@@ -1236,7 +1356,7 @@
     <t>bond_overload</t>
   </si>
   <si>
-    <t>谢博机械×物资哥能源：同场解锁融合技</t>
+    <t>机械×能源同场：工牌亮了才能开这手兄弟连招。</t>
   </si>
   <si>
     <t>Mechanical|Energy</t>
@@ -1248,7 +1368,7 @@
     <t>bond_joint_inspection</t>
   </si>
   <si>
-    <t>土木×公共治理：施工区控场并提供团队安全护具</t>
+    <t>土木×公职同场：施工区控场，护具先发再扯皮。</t>
   </si>
   <si>
     <t>Civil|Official</t>
@@ -1257,7 +1377,7 @@
     <t>bond_supply_chain</t>
   </si>
   <si>
-    <t>创业×能源：渠道接通产能，临时扩充生产队伍</t>
+    <t>创业×能源同场：渠道一接上，人就多一个。</t>
   </si>
   <si>
     <t>Startup|Energy</t>
@@ -1637,19 +1757,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:AD39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="13.571428571428571" customWidth="1"/>
     <col min="2" max="2" width="20.428571428571427" customWidth="1"/>
     <col min="3" max="3" width="16.714285714285715" customWidth="1"/>
     <col min="4" max="4" width="13.571428571428571" customWidth="1"/>
-    <col min="5" max="5" width="49.42857142857143" customWidth="1"/>
-    <col min="6" max="6" width="48.714285714285715" customWidth="1"/>
-    <col min="7" max="25" width="13.571428571428571" customWidth="1"/>
+    <col min="5" max="6" width="42.142857142857146" customWidth="1"/>
+    <col min="7" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1745,7 +1864,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>24</v>
       </c>
@@ -1771,7 +1890,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>31</v>
       </c>
@@ -1797,7 +1916,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>38</v>
       </c>
@@ -1823,7 +1942,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>43</v>
       </c>
@@ -1849,7 +1968,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>49</v>
       </c>
@@ -1875,7 +1994,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>55</v>
       </c>
@@ -1901,7 +2020,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>60</v>
       </c>
@@ -1927,7 +2046,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>65</v>
       </c>
@@ -1953,7 +2072,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>72</v>
       </c>
@@ -1979,7 +2098,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>78</v>
       </c>
@@ -2008,7 +2127,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>85</v>
       </c>
@@ -2034,7 +2153,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>90</v>
       </c>
@@ -2063,7 +2182,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>97</v>
       </c>
@@ -2089,7 +2208,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>103</v>
       </c>
@@ -2115,7 +2234,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>109</v>
       </c>
@@ -2141,7 +2260,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>114</v>
       </c>
@@ -2167,7 +2286,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>120</v>
       </c>
@@ -2193,7 +2312,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>125</v>
       </c>
@@ -2219,7 +2338,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>131</v>
       </c>
@@ -2245,7 +2364,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>136</v>
       </c>
@@ -2271,7 +2390,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>143</v>
       </c>
@@ -2297,7 +2416,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>149</v>
       </c>
@@ -2323,7 +2442,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>156</v>
       </c>
@@ -2346,7 +2465,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>161</v>
       </c>
@@ -2369,7 +2488,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>165</v>
       </c>
@@ -2392,7 +2511,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>169</v>
       </c>
@@ -2421,7 +2540,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>176</v>
       </c>
@@ -2450,7 +2569,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>182</v>
       </c>
@@ -2467,13 +2586,13 @@
         <v>185</v>
       </c>
       <c r="G31" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H31" t="s">
         <v>186</v>
       </c>
       <c r="I31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J31" t="s">
         <v>187</v>
@@ -2484,9 +2603,12 @@
         <v>188</v>
       </c>
       <c r="C32" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" t="s">
         <v>189</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>190</v>
       </c>
       <c r="F32" t="s">
@@ -2499,7 +2621,7 @@
         <v>192</v>
       </c>
       <c r="I32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J32" t="s">
         <v>193</v>
@@ -2525,7 +2647,7 @@
         <v>198</v>
       </c>
       <c r="I33">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J33" t="s">
         <v>199</v>
@@ -2551,7 +2673,7 @@
         <v>204</v>
       </c>
       <c r="I34">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J34" t="s">
         <v>205</v>
@@ -2562,51 +2684,129 @@
         <v>206</v>
       </c>
       <c r="C35" t="s">
-        <v>150</v>
+        <v>207</v>
       </c>
       <c r="D35" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F35" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G35" t="s">
-        <v>153</v>
+        <v>35</v>
       </c>
       <c r="H35" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I35">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J35" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C36" t="s">
         <v>150</v>
       </c>
       <c r="D36" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F36" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G36" t="s">
         <v>153</v>
       </c>
       <c r="H36" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I36">
+        <v>17</v>
+      </c>
+      <c r="J36" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>217</v>
+      </c>
+      <c r="C37" t="s">
+        <v>150</v>
+      </c>
+      <c r="D37" t="s">
+        <v>218</v>
+      </c>
+      <c r="F37" t="s">
+        <v>219</v>
+      </c>
+      <c r="G37" t="s">
+        <v>153</v>
+      </c>
+      <c r="H37" t="s">
+        <v>220</v>
+      </c>
+      <c r="I37">
         <v>19</v>
       </c>
-      <c r="J36" t="s">
-        <v>215</v>
+      <c r="J37" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>222</v>
+      </c>
+      <c r="C38" t="s">
+        <v>223</v>
+      </c>
+      <c r="D38" t="s">
+        <v>224</v>
+      </c>
+      <c r="F38" t="s">
+        <v>225</v>
+      </c>
+      <c r="G38" t="s">
+        <v>35</v>
+      </c>
+      <c r="H38" t="s">
+        <v>226</v>
+      </c>
+      <c r="I38">
+        <v>8</v>
+      </c>
+      <c r="J38" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>228</v>
+      </c>
+      <c r="C39" t="s">
+        <v>229</v>
+      </c>
+      <c r="D39" t="s">
+        <v>230</v>
+      </c>
+      <c r="F39" t="s">
+        <v>231</v>
+      </c>
+      <c r="G39" t="s">
+        <v>140</v>
+      </c>
+      <c r="H39" t="s">
+        <v>232</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -2617,7 +2817,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N53"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
@@ -2631,40 +2831,40 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="D1" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="E1" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="F1" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="G1" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="H1" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="I1" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="J1" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="K1" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="L1" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="M1" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="N1" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -2675,10 +2875,10 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="D2" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
@@ -2693,7 +2893,7 @@
         <v>14</v>
       </c>
       <c r="I2" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="J2" t="s">
         <v>11</v>
@@ -2719,40 +2919,40 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="D3" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="E3" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="F3" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="G3" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="H3" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="I3" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="J3" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="K3" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="L3" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="M3" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="N3" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.25">
@@ -2760,10 +2960,10 @@
         <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="E4">
         <v>0.15</v>
@@ -2781,16 +2981,16 @@
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="L4" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="M4" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="N4" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.25">
@@ -2798,10 +2998,10 @@
         <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="D5" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -2819,27 +3019,27 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="L5" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="M5" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="N5" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="C6" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="D6" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="E6">
         <v>0.25</v>
@@ -2857,27 +3057,27 @@
         <v>3</v>
       </c>
       <c r="K6" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="L6" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="M6" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="N6" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="C7" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="D7" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="E7">
         <v>8</v>
@@ -2895,27 +3095,27 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="L7" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="M7" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="N7" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="C8" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="D8" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="E8">
         <v>-0.35</v>
@@ -2933,27 +3133,27 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="L8" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="M8" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="N8" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="C9" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="D9" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="E9">
         <v>0.4</v>
@@ -2971,27 +3171,27 @@
         <v>5</v>
       </c>
       <c r="K9" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="L9" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="M9" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="N9" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="C10" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="D10" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -3009,27 +3209,27 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="L10" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="M10" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="N10" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="C11" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="D11" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -3047,16 +3247,16 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="L11" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="M11" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="N11" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
@@ -3064,10 +3264,10 @@
         <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="D12" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="E12">
         <v>12</v>
@@ -3085,27 +3285,27 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="L12" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="M12" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="N12" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="C13" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="D13" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="E13">
         <v>0.35</v>
@@ -3123,27 +3323,27 @@
         <v>6</v>
       </c>
       <c r="K13" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="L13" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="M13" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="N13" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="C14" t="s">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="D14" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -3164,16 +3364,16 @@
         <v>137</v>
       </c>
       <c r="K14" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="L14" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="M14" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="N14" t="s">
-        <v>290</v>
+        <v>307</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -3181,10 +3381,10 @@
         <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="D15" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="E15">
         <v>0.15</v>
@@ -3202,24 +3402,24 @@
         <v>2</v>
       </c>
       <c r="K15" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="M15" t="s">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="N15" t="s">
-        <v>67</v>
+        <v>311</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>76</v>
+        <v>312</v>
       </c>
       <c r="C16" t="s">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="E16">
         <v>20</v>
@@ -3237,16 +3437,16 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
       <c r="L16" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
       <c r="M16" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="N16" t="s">
-        <v>74</v>
+        <v>316</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -3254,10 +3454,10 @@
         <v>95</v>
       </c>
       <c r="C17" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="D17" t="s">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="E17">
         <v>18</v>
@@ -3275,27 +3475,27 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="L17" t="s">
-        <v>299</v>
+        <v>319</v>
       </c>
       <c r="M17" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="N17" t="s">
-        <v>92</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="C18" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="D18" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="E18">
         <v>-0.4</v>
@@ -3313,27 +3513,27 @@
         <v>7</v>
       </c>
       <c r="K18" t="s">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="L18" t="s">
-        <v>302</v>
+        <v>323</v>
       </c>
       <c r="M18" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="N18" t="s">
-        <v>303</v>
+        <v>324</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="C19" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="D19" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="E19">
         <v>0.25</v>
@@ -3351,27 +3551,27 @@
         <v>8</v>
       </c>
       <c r="K19" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="L19" t="s">
-        <v>302</v>
+        <v>323</v>
       </c>
       <c r="M19" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="N19" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="C20" t="s">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="D20" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="E20">
         <v>15</v>
@@ -3389,24 +3589,24 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
       <c r="M20" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="N20" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="C21" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="D21" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="E21">
         <v>10</v>
@@ -3424,13 +3624,13 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="M21" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="N21" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
@@ -3438,10 +3638,10 @@
         <v>141</v>
       </c>
       <c r="C22" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="D22" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="E22">
         <v>8</v>
@@ -3459,16 +3659,16 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="L22" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="M22" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="N22" t="s">
-        <v>139</v>
+        <v>333</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
@@ -3476,10 +3676,10 @@
         <v>147</v>
       </c>
       <c r="C23" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="D23" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="E23">
         <v>6</v>
@@ -3497,16 +3697,16 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="L23" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="M23" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="N23" t="s">
-        <v>146</v>
+        <v>334</v>
       </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.25">
@@ -3514,10 +3714,10 @@
         <v>107</v>
       </c>
       <c r="C24" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="D24" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="E24">
         <v>14</v>
@@ -3535,16 +3735,16 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="L24" t="s">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="M24" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="N24" t="s">
-        <v>314</v>
+        <v>337</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.25">
@@ -3552,10 +3752,10 @@
         <v>112</v>
       </c>
       <c r="C25" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="D25" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="E25">
         <v>0.08</v>
@@ -3573,13 +3773,13 @@
         <v>9</v>
       </c>
       <c r="K25" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="M25" t="s">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="N25" t="s">
-        <v>316</v>
+        <v>339</v>
       </c>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.25">
@@ -3587,10 +3787,10 @@
         <v>118</v>
       </c>
       <c r="C26" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="D26" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="E26">
         <v>0.18</v>
@@ -3608,16 +3808,16 @@
         <v>10</v>
       </c>
       <c r="K26" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="L26" t="s">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="M26" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="N26" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.25">
@@ -3625,10 +3825,10 @@
         <v>123</v>
       </c>
       <c r="C27" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="D27" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="E27">
         <v>22</v>
@@ -3646,16 +3846,16 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>319</v>
+        <v>342</v>
       </c>
       <c r="L27" t="s">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="M27" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="N27" t="s">
-        <v>320</v>
+        <v>343</v>
       </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.25">
@@ -3663,10 +3863,10 @@
         <v>129</v>
       </c>
       <c r="C28" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="E28">
         <v>0.22</v>
@@ -3683,31 +3883,28 @@
       <c r="I28">
         <v>11</v>
       </c>
-      <c r="J28" t="s">
-        <v>321</v>
-      </c>
       <c r="K28" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="L28" t="s">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="M28" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="N28" t="s">
-        <v>324</v>
+        <v>346</v>
       </c>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>325</v>
+        <v>347</v>
       </c>
       <c r="C29" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="E29">
         <v>10</v>
@@ -3724,31 +3921,28 @@
       <c r="I29">
         <v>0</v>
       </c>
-      <c r="J29" t="s">
-        <v>321</v>
-      </c>
       <c r="K29" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="L29" t="s">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="M29" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="N29" t="s">
-        <v>327</v>
+        <v>349</v>
       </c>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="C30" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="D30" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -3765,20 +3959,17 @@
       <c r="I30">
         <v>0</v>
       </c>
-      <c r="J30" t="s">
-        <v>321</v>
-      </c>
       <c r="K30" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="L30" t="s">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="M30" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="N30" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.25">
@@ -3786,10 +3977,10 @@
         <v>154</v>
       </c>
       <c r="C31" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="D31" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="E31">
         <v>0.3</v>
@@ -3807,16 +3998,16 @@
         <v>12</v>
       </c>
       <c r="K31" t="s">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="L31" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="M31" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="N31" t="s">
-        <v>151</v>
+        <v>354</v>
       </c>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.25">
@@ -3824,10 +4015,10 @@
         <v>160</v>
       </c>
       <c r="C32" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="D32" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -3845,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>332</v>
+        <v>355</v>
       </c>
       <c r="N32" t="s">
-        <v>333</v>
+        <v>356</v>
       </c>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.25">
@@ -3856,10 +4047,10 @@
         <v>164</v>
       </c>
       <c r="C33" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="D33" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="E33">
         <v>0.16</v>
@@ -3877,10 +4068,10 @@
         <v>2101</v>
       </c>
       <c r="K33" t="s">
-        <v>334</v>
+        <v>357</v>
       </c>
       <c r="N33" t="s">
-        <v>333</v>
+        <v>356</v>
       </c>
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.25">
@@ -3888,10 +4079,10 @@
         <v>168</v>
       </c>
       <c r="C34" t="s">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="D34" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="E34">
         <v>12</v>
@@ -3909,21 +4100,21 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>335</v>
+        <v>358</v>
       </c>
       <c r="N34" t="s">
-        <v>333</v>
+        <v>356</v>
       </c>
     </row>
     <row r="35" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>336</v>
+        <v>359</v>
       </c>
       <c r="C35" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="E35">
         <v>14</v>
@@ -3940,31 +4131,28 @@
       <c r="I35">
         <v>0</v>
       </c>
-      <c r="J35" t="s">
-        <v>321</v>
-      </c>
       <c r="K35" t="s">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="L35" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="M35" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="N35" t="s">
-        <v>338</v>
+        <v>361</v>
       </c>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>339</v>
+        <v>362</v>
       </c>
       <c r="C36" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="D36" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="E36">
         <v>28</v>
@@ -3981,31 +4169,25 @@
       <c r="I36">
         <v>0</v>
       </c>
-      <c r="J36" t="s">
-        <v>321</v>
-      </c>
       <c r="K36" t="s">
-        <v>340</v>
-      </c>
-      <c r="L36" t="s">
-        <v>321</v>
+        <v>363</v>
       </c>
       <c r="M36" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="N36" t="s">
-        <v>341</v>
+        <v>364</v>
       </c>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>342</v>
+        <v>365</v>
       </c>
       <c r="C37" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="D37" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="E37">
         <v>10</v>
@@ -4022,31 +4204,28 @@
       <c r="I37">
         <v>0</v>
       </c>
-      <c r="J37" t="s">
-        <v>321</v>
-      </c>
       <c r="K37" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="L37" t="s">
-        <v>344</v>
+        <v>367</v>
       </c>
       <c r="M37" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="N37" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>346</v>
+        <v>369</v>
       </c>
       <c r="C38" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="D38" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="E38">
         <v>0.12</v>
@@ -4063,31 +4242,25 @@
       <c r="I38">
         <v>14</v>
       </c>
-      <c r="J38" t="s">
-        <v>321</v>
-      </c>
       <c r="K38" t="s">
-        <v>347</v>
-      </c>
-      <c r="L38" t="s">
-        <v>321</v>
+        <v>370</v>
       </c>
       <c r="M38" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="N38" t="s">
-        <v>348</v>
+        <v>371</v>
       </c>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>349</v>
+        <v>372</v>
       </c>
       <c r="C39" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="D39" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -4104,31 +4277,28 @@
       <c r="I39">
         <v>0</v>
       </c>
-      <c r="J39" t="s">
-        <v>321</v>
-      </c>
       <c r="K39" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="L39" t="s">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="M39" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="N39" t="s">
-        <v>352</v>
+        <v>375</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="C40" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="D40" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="E40">
         <v>0.2</v>
@@ -4145,31 +4315,25 @@
       <c r="I40">
         <v>15</v>
       </c>
-      <c r="J40" t="s">
-        <v>321</v>
-      </c>
       <c r="K40" t="s">
-        <v>354</v>
-      </c>
-      <c r="L40" t="s">
-        <v>321</v>
+        <v>377</v>
       </c>
       <c r="M40" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="N40" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>356</v>
+        <v>379</v>
       </c>
       <c r="C41" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="D41" t="s">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="E41">
         <v>-0.3</v>
@@ -4186,31 +4350,28 @@
       <c r="I41">
         <v>16</v>
       </c>
-      <c r="J41" t="s">
-        <v>321</v>
-      </c>
       <c r="K41" t="s">
-        <v>357</v>
+        <v>380</v>
       </c>
       <c r="L41" t="s">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="M41" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="N41" t="s">
-        <v>359</v>
+        <v>382</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="C42" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="D42" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="E42">
         <v>0.25</v>
@@ -4227,31 +4388,25 @@
       <c r="I42">
         <v>17</v>
       </c>
-      <c r="J42" t="s">
-        <v>321</v>
-      </c>
       <c r="K42" t="s">
-        <v>361</v>
-      </c>
-      <c r="L42" t="s">
-        <v>321</v>
+        <v>384</v>
       </c>
       <c r="M42" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="N42" t="s">
-        <v>362</v>
+        <v>385</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="C43" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="D43" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="E43">
         <v>0.12</v>
@@ -4268,31 +4423,28 @@
       <c r="I43">
         <v>18</v>
       </c>
-      <c r="J43" t="s">
-        <v>321</v>
-      </c>
       <c r="K43" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="L43" t="s">
-        <v>344</v>
+        <v>367</v>
       </c>
       <c r="M43" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="N43" t="s">
-        <v>365</v>
+        <v>388</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>366</v>
+        <v>389</v>
       </c>
       <c r="C44" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="D44" t="s">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="E44">
         <v>-0.28</v>
@@ -4309,31 +4461,28 @@
       <c r="I44">
         <v>19</v>
       </c>
-      <c r="J44" t="s">
-        <v>321</v>
-      </c>
       <c r="K44" t="s">
-        <v>367</v>
+        <v>390</v>
       </c>
       <c r="L44" t="s">
-        <v>368</v>
+        <v>391</v>
       </c>
       <c r="M44" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="N44" t="s">
-        <v>369</v>
+        <v>392</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>370</v>
+        <v>393</v>
       </c>
       <c r="C45" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="D45" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="E45">
         <v>10</v>
@@ -4350,31 +4499,25 @@
       <c r="I45">
         <v>0</v>
       </c>
-      <c r="J45" t="s">
-        <v>321</v>
-      </c>
       <c r="K45" t="s">
-        <v>371</v>
-      </c>
-      <c r="L45" t="s">
-        <v>321</v>
+        <v>394</v>
       </c>
       <c r="M45" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="N45" t="s">
-        <v>372</v>
+        <v>395</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>373</v>
+        <v>396</v>
       </c>
       <c r="C46" t="s">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="D46" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="E46">
         <v>1</v>
@@ -4395,27 +4538,27 @@
         <v>144</v>
       </c>
       <c r="K46" t="s">
-        <v>374</v>
+        <v>397</v>
       </c>
       <c r="L46" t="s">
-        <v>368</v>
+        <v>391</v>
       </c>
       <c r="M46" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="N46" t="s">
-        <v>375</v>
+        <v>398</v>
       </c>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>376</v>
+        <v>399</v>
       </c>
       <c r="C47" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="D47" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="E47">
         <v>0.12</v>
@@ -4432,31 +4575,28 @@
       <c r="I47">
         <v>20</v>
       </c>
-      <c r="J47" t="s">
-        <v>321</v>
-      </c>
       <c r="K47" t="s">
-        <v>377</v>
+        <v>400</v>
       </c>
       <c r="L47" t="s">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="M47" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="N47" t="s">
-        <v>378</v>
+        <v>401</v>
       </c>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>379</v>
+        <v>402</v>
       </c>
       <c r="C48" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="D48" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="E48">
         <v>16</v>
@@ -4473,31 +4613,28 @@
       <c r="I48">
         <v>0</v>
       </c>
-      <c r="J48" t="s">
-        <v>321</v>
-      </c>
       <c r="K48" t="s">
-        <v>380</v>
+        <v>403</v>
       </c>
       <c r="L48" t="s">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="M48" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="N48" t="s">
-        <v>382</v>
+        <v>405</v>
       </c>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>383</v>
+        <v>406</v>
       </c>
       <c r="C49" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="D49" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="E49">
         <v>0.16</v>
@@ -4514,31 +4651,28 @@
       <c r="I49">
         <v>21</v>
       </c>
-      <c r="J49" t="s">
-        <v>321</v>
-      </c>
       <c r="K49" t="s">
-        <v>384</v>
+        <v>407</v>
       </c>
       <c r="L49" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="M49" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="N49" t="s">
-        <v>385</v>
+        <v>408</v>
       </c>
     </row>
     <row r="50" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>386</v>
+        <v>409</v>
       </c>
       <c r="C50" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="D50" t="s">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="E50">
         <v>-0.3</v>
@@ -4555,31 +4689,28 @@
       <c r="I50">
         <v>22</v>
       </c>
-      <c r="J50" t="s">
-        <v>321</v>
-      </c>
       <c r="K50" t="s">
-        <v>387</v>
+        <v>410</v>
       </c>
       <c r="L50" t="s">
-        <v>302</v>
+        <v>323</v>
       </c>
       <c r="M50" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="N50" t="s">
-        <v>388</v>
+        <v>411</v>
       </c>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>389</v>
+        <v>412</v>
       </c>
       <c r="C51" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="D51" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="E51">
         <v>14</v>
@@ -4596,31 +4727,25 @@
       <c r="I51">
         <v>0</v>
       </c>
-      <c r="J51" t="s">
-        <v>321</v>
-      </c>
       <c r="K51" t="s">
-        <v>390</v>
-      </c>
-      <c r="L51" t="s">
-        <v>321</v>
+        <v>413</v>
       </c>
       <c r="M51" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="N51" t="s">
-        <v>391</v>
+        <v>414</v>
       </c>
     </row>
     <row r="52" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>392</v>
+        <v>415</v>
       </c>
       <c r="C52" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="D52" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="E52">
         <v>0.25</v>
@@ -4637,31 +4762,28 @@
       <c r="I52">
         <v>23</v>
       </c>
-      <c r="J52" t="s">
-        <v>321</v>
-      </c>
       <c r="K52" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="L52" t="s">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="M52" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="N52" t="s">
-        <v>394</v>
+        <v>417</v>
       </c>
     </row>
     <row r="53" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>395</v>
+        <v>418</v>
       </c>
       <c r="C53" t="s">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="D53" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -4682,16 +4804,262 @@
         <v>144</v>
       </c>
       <c r="K53" t="s">
+        <v>397</v>
+      </c>
+      <c r="L53" t="s">
+        <v>391</v>
+      </c>
+      <c r="M53" t="s">
+        <v>282</v>
+      </c>
+      <c r="N53" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="54" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>420</v>
+      </c>
+      <c r="C54" t="s">
+        <v>260</v>
+      </c>
+      <c r="D54" t="s">
+        <v>261</v>
+      </c>
+      <c r="E54">
+        <v>0.1</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="G54">
+        <v>8</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>21</v>
+      </c>
+      <c r="J54" t="s">
+        <v>421</v>
+      </c>
+      <c r="K54" t="s">
+        <v>422</v>
+      </c>
+      <c r="L54" t="s">
+        <v>423</v>
+      </c>
+      <c r="M54" t="s">
+        <v>264</v>
+      </c>
+      <c r="N54" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="55" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>425</v>
+      </c>
+      <c r="C55" t="s">
+        <v>266</v>
+      </c>
+      <c r="D55" t="s">
+        <v>267</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>1.24</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55" t="s">
+        <v>421</v>
+      </c>
+      <c r="K55" t="s">
+        <v>426</v>
+      </c>
+      <c r="L55" t="s">
         <v>374</v>
       </c>
-      <c r="L53" t="s">
-        <v>368</v>
-      </c>
-      <c r="M53" t="s">
-        <v>265</v>
-      </c>
-      <c r="N53" t="s">
-        <v>396</v>
+      <c r="M55" t="s">
+        <v>270</v>
+      </c>
+      <c r="N55" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="56" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>428</v>
+      </c>
+      <c r="C56" t="s">
+        <v>295</v>
+      </c>
+      <c r="D56" t="s">
+        <v>261</v>
+      </c>
+      <c r="E56">
+        <v>22</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56" t="s">
+        <v>421</v>
+      </c>
+      <c r="K56" t="s">
+        <v>429</v>
+      </c>
+      <c r="L56" t="s">
+        <v>336</v>
+      </c>
+      <c r="M56" t="s">
+        <v>264</v>
+      </c>
+      <c r="N56" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="57" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>431</v>
+      </c>
+      <c r="C57" t="s">
+        <v>266</v>
+      </c>
+      <c r="D57" t="s">
+        <v>267</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>1.2</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57" t="s">
+        <v>421</v>
+      </c>
+      <c r="K57" t="s">
+        <v>432</v>
+      </c>
+      <c r="L57" t="s">
+        <v>323</v>
+      </c>
+      <c r="M57" t="s">
+        <v>282</v>
+      </c>
+      <c r="N57" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="58" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>232</v>
+      </c>
+      <c r="C58" t="s">
+        <v>266</v>
+      </c>
+      <c r="D58" t="s">
+        <v>267</v>
+      </c>
+      <c r="E58">
+        <v>5</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58" t="s">
+        <v>421</v>
+      </c>
+      <c r="K58" t="s">
+        <v>332</v>
+      </c>
+      <c r="L58" t="s">
+        <v>269</v>
+      </c>
+      <c r="M58" t="s">
+        <v>270</v>
+      </c>
+      <c r="N58" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="59" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>435</v>
+      </c>
+      <c r="C59" t="s">
+        <v>304</v>
+      </c>
+      <c r="D59" t="s">
+        <v>261</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59">
+        <v>12</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59" t="s">
+        <v>229</v>
+      </c>
+      <c r="K59" t="s">
+        <v>305</v>
+      </c>
+      <c r="L59" t="s">
+        <v>391</v>
+      </c>
+      <c r="M59" t="s">
+        <v>282</v>
+      </c>
+      <c r="N59" t="s">
+        <v>436</v>
       </c>
     </row>
   </sheetData>
@@ -4702,13 +5070,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:AD6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4722,13 +5090,13 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
-        <v>397</v>
+        <v>437</v>
       </c>
       <c r="F1" t="s">
-        <v>398</v>
+        <v>438</v>
       </c>
       <c r="G1" t="s">
-        <v>399</v>
+        <v>439</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -4745,10 +5113,10 @@
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="F2" t="s">
-        <v>401</v>
+        <v>441</v>
       </c>
       <c r="G2" t="s">
         <v>11</v>
@@ -4759,7 +5127,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>402</v>
+        <v>442</v>
       </c>
       <c r="C3" t="s">
         <v>17</v>
@@ -4768,30 +5136,30 @@
         <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>403</v>
+        <v>443</v>
       </c>
       <c r="F3" t="s">
-        <v>404</v>
+        <v>444</v>
       </c>
       <c r="G3" t="s">
-        <v>405</v>
+        <v>445</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>406</v>
+        <v>446</v>
       </c>
       <c r="C4" t="s">
         <v>151</v>
       </c>
       <c r="D4" t="s">
-        <v>407</v>
+        <v>447</v>
       </c>
       <c r="E4" t="s">
-        <v>408</v>
+        <v>448</v>
       </c>
       <c r="F4" t="s">
-        <v>409</v>
+        <v>449</v>
       </c>
       <c r="G4" t="s">
         <v>149</v>
@@ -4799,42 +5167,42 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>410</v>
+        <v>450</v>
       </c>
       <c r="C5" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D5" t="s">
-        <v>411</v>
+        <v>451</v>
       </c>
       <c r="E5" t="s">
-        <v>412</v>
-      </c>
-      <c r="F5" t="b">
-        <v>1</v>
+        <v>452</v>
+      </c>
+      <c r="F5" t="s">
+        <v>449</v>
       </c>
       <c r="G5" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>413</v>
+        <v>453</v>
       </c>
       <c r="C6" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D6" t="s">
-        <v>414</v>
+        <v>454</v>
       </c>
       <c r="E6" t="s">
-        <v>415</v>
-      </c>
-      <c r="F6" t="b">
-        <v>1</v>
+        <v>455</v>
+      </c>
+      <c r="F6" t="s">
+        <v>449</v>
       </c>
       <c r="G6" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
